--- a/data/salary day.xlsx
+++ b/data/salary day.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4th year\sem 2\EEX5362 Perfomance Modeling\Miniproject\github\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15336" windowHeight="5424"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="salary day" sheetId="1" r:id="rId4"/>
+    <sheet name="salary day" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="7">
   <si>
     <t>customerId</t>
   </si>
@@ -37,55 +45,70 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -275,17 +298,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -305,78 +338,78 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>6.5</v>
       </c>
       <c r="C4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
         <v>0.5</v>
       </c>
       <c r="D5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
         <v>3.5</v>
@@ -385,18 +418,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>0.5</v>
       </c>
       <c r="D6" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1">
         <v>7.5</v>
@@ -405,35 +438,35 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>14.5</v>
       </c>
       <c r="C8" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1">
         <v>5.5</v>
@@ -445,158 +478,158 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1">
         <v>3.5</v>
       </c>
       <c r="D16" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1">
         <v>7.5</v>
@@ -605,207 +638,768 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D18" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E18" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D19" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E22" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="C23" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D23" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E23" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D24" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E25" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="1">
-        <v>58.0</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="D26" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="E26" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="F26" s="1" t="s">
+    <row r="26" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>59.9</v>
+      </c>
+      <c r="C27">
+        <v>3.1</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
+        <v>9.1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>63.5</v>
+      </c>
+      <c r="C28">
+        <v>1.5</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>4.5</v>
+      </c>
+      <c r="F28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>67.2</v>
+      </c>
+      <c r="C29">
+        <v>0.8</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29">
+        <v>7.8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>69.8</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+      <c r="E30">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="C31">
+        <v>2.1</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>7.1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="C32">
+        <v>0.2</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>3.2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>79.3</v>
+      </c>
+      <c r="C33">
+        <v>0.5</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>4.5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>81.5</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>7</v>
+      </c>
+      <c r="E34">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>86</v>
+      </c>
+      <c r="C36">
+        <v>2.5</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>9.5</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>88.2</v>
+      </c>
+      <c r="C37">
+        <v>1.8</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+      <c r="E37">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>92.2</v>
+      </c>
+      <c r="C38">
+        <v>3.3</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>6.3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>95.1</v>
+      </c>
+      <c r="C39">
+        <v>2.9</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>7.9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>98.7</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>101.7</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>104.3</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>7</v>
+      </c>
+      <c r="E42">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>106.3</v>
+      </c>
+      <c r="C43">
+        <v>1.4</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>108.8</v>
+      </c>
+      <c r="C44">
+        <v>1.9</v>
+      </c>
+      <c r="D44">
+        <v>8</v>
+      </c>
+      <c r="E44">
+        <v>9.9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>112.3</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>7</v>
+      </c>
+      <c r="E45">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>115</v>
+      </c>
+      <c r="C46">
+        <v>3.7</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>7.7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>117.7</v>
+      </c>
+      <c r="C47">
+        <v>1.6</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47">
+        <v>6.6</v>
+      </c>
+      <c r="F47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>120.2</v>
+      </c>
+      <c r="C48">
+        <v>2.5</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+      <c r="E48">
+        <v>8.5</v>
+      </c>
+      <c r="F48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>122.8</v>
+      </c>
+      <c r="C49">
+        <v>1.5</v>
+      </c>
+      <c r="D49">
+        <v>8</v>
+      </c>
+      <c r="E49">
+        <v>9.5</v>
+      </c>
+      <c r="F49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>126.7</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>129.19999999999999</v>
+      </c>
+      <c r="C51">
+        <v>3.1</v>
+      </c>
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51">
+        <v>8.1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>132.69999999999999</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <v>6</v>
+      </c>
+      <c r="E52">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>135.30000000000001</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>7</v>
+      </c>
+      <c r="E53">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="C54">
+        <v>3.4</v>
+      </c>
+      <c r="D54">
+        <v>7</v>
+      </c>
+      <c r="E54">
+        <v>10.4</v>
+      </c>
+      <c r="F54" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/salary day.xlsx
+++ b/data/salary day.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="7">
   <si>
     <t>customerId</t>
   </si>
@@ -60,7 +60,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -70,6 +70,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -86,10 +92,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -308,7 +316,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -318,7 +326,7 @@
     <col min="5" max="5" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -338,7 +346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -358,7 +366,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -378,7 +386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -398,7 +406,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -418,7 +426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -438,7 +446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -458,7 +466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -478,7 +486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -498,7 +506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -518,7 +526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -538,7 +546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -558,7 +566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -578,7 +586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -598,7 +606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -618,7 +626,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -638,7 +646,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -658,7 +666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -678,7 +686,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -698,7 +706,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -718,7 +726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -738,7 +746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -758,7 +766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -778,7 +786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -798,7 +806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1379,22 +1387,1082 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54">
+      <c r="A54" s="4">
         <v>53</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="4">
         <v>139.30000000000001</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="4">
         <v>3.4</v>
       </c>
-      <c r="D54">
-        <v>7</v>
-      </c>
-      <c r="E54">
+      <c r="D54" s="4">
+        <v>7</v>
+      </c>
+      <c r="E54" s="4">
         <v>10.4</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>142.1</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>144.5</v>
+      </c>
+      <c r="C56">
+        <v>0.5</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="E56">
+        <v>6.5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="C57">
+        <v>1.2</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57">
+        <v>6.2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>149</v>
+      </c>
+      <c r="C58">
+        <v>2.5</v>
+      </c>
+      <c r="D58">
+        <v>7</v>
+      </c>
+      <c r="E58">
+        <v>9.5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>151.4</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59">
+        <v>7</v>
+      </c>
+      <c r="F59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>153.6</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>4</v>
+      </c>
+      <c r="F60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>5</v>
+      </c>
+      <c r="F61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>158.5</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>8</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+      <c r="F62" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>160.69999999999999</v>
+      </c>
+      <c r="C63">
+        <v>0.8</v>
+      </c>
+      <c r="D63">
+        <v>6</v>
+      </c>
+      <c r="E63">
+        <v>6.8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>163.1</v>
+      </c>
+      <c r="C64">
+        <v>1.5</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>5.5</v>
+      </c>
+      <c r="F64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>165.4</v>
+      </c>
+      <c r="C65">
+        <v>3.2</v>
+      </c>
+      <c r="D65">
+        <v>7</v>
+      </c>
+      <c r="E65">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F65" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>167.9</v>
+      </c>
+      <c r="C66">
+        <v>4.5</v>
+      </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+      <c r="E66">
+        <v>9.5</v>
+      </c>
+      <c r="F66" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>170.2</v>
+      </c>
+      <c r="C67">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D67">
+        <v>6</v>
+      </c>
+      <c r="E67">
+        <v>11.1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>172.6</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>6</v>
+      </c>
+      <c r="F68" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>174.9</v>
+      </c>
+      <c r="C69">
+        <v>1.5</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69">
+        <v>6.5</v>
+      </c>
+      <c r="F69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>177.3</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>7</v>
+      </c>
+      <c r="E70">
+        <v>7</v>
+      </c>
+      <c r="F70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>179.8</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>182.1</v>
+      </c>
+      <c r="C72">
+        <v>0.5</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <v>6.5</v>
+      </c>
+      <c r="F72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>184.4</v>
+      </c>
+      <c r="C73">
+        <v>1.8</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <v>6.8</v>
+      </c>
+      <c r="F73" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>186.7</v>
+      </c>
+      <c r="C74">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D74">
+        <v>8</v>
+      </c>
+      <c r="E74">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>189.2</v>
+      </c>
+      <c r="C75">
+        <v>3.5</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
+        <v>6.5</v>
+      </c>
+      <c r="F75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>191.6</v>
+      </c>
+      <c r="C76">
+        <v>4</v>
+      </c>
+      <c r="D76">
+        <v>7</v>
+      </c>
+      <c r="E76">
+        <v>11</v>
+      </c>
+      <c r="F76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>193.9</v>
+      </c>
+      <c r="C77">
+        <v>2.5</v>
+      </c>
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="E77">
+        <v>6.5</v>
+      </c>
+      <c r="F77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3">
+        <v>196.3</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3">
+        <v>5</v>
+      </c>
+      <c r="E78" s="3">
+        <v>6</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>198.7</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>6</v>
+      </c>
+      <c r="E79">
+        <v>6</v>
+      </c>
+      <c r="F79" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>201</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>203.4</v>
+      </c>
+      <c r="C81">
+        <v>0.2</v>
+      </c>
+      <c r="D81">
+        <v>8</v>
+      </c>
+      <c r="E81">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F81" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>205.8</v>
+      </c>
+      <c r="C82">
+        <v>1.4</v>
+      </c>
+      <c r="D82">
+        <v>7</v>
+      </c>
+      <c r="E82">
+        <v>8.4</v>
+      </c>
+      <c r="F82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>208.1</v>
+      </c>
+      <c r="C83">
+        <v>2.8</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>6.8</v>
+      </c>
+      <c r="F83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>210.5</v>
+      </c>
+      <c r="C84">
+        <v>3.1</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <v>8.1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>212.9</v>
+      </c>
+      <c r="C85">
+        <v>4.2</v>
+      </c>
+      <c r="D85">
+        <v>6</v>
+      </c>
+      <c r="E85">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>215.2</v>
+      </c>
+      <c r="C86">
+        <v>2.5</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+      <c r="E86">
+        <v>5.5</v>
+      </c>
+      <c r="F86" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>217.6</v>
+      </c>
+      <c r="C87">
+        <v>1.2</v>
+      </c>
+      <c r="D87">
+        <v>7</v>
+      </c>
+      <c r="E87">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>220.1</v>
+      </c>
+      <c r="C88">
+        <v>0.5</v>
+      </c>
+      <c r="D88">
+        <v>5</v>
+      </c>
+      <c r="E88">
+        <v>5.5</v>
+      </c>
+      <c r="F88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>222.5</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89">
+        <v>4</v>
+      </c>
+      <c r="F89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>224.8</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>6</v>
+      </c>
+      <c r="E90">
+        <v>6</v>
+      </c>
+      <c r="F90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>227.2</v>
+      </c>
+      <c r="C91">
+        <v>1.5</v>
+      </c>
+      <c r="D91">
+        <v>8</v>
+      </c>
+      <c r="E91">
+        <v>9.5</v>
+      </c>
+      <c r="F91" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>229.6</v>
+      </c>
+      <c r="C92">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>5.3</v>
+      </c>
+      <c r="F92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>232</v>
+      </c>
+      <c r="C93">
+        <v>3.8</v>
+      </c>
+      <c r="D93">
+        <v>5</v>
+      </c>
+      <c r="E93">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>234.3</v>
+      </c>
+      <c r="C94">
+        <v>4.5</v>
+      </c>
+      <c r="D94">
+        <v>7</v>
+      </c>
+      <c r="E94">
+        <v>11.5</v>
+      </c>
+      <c r="F94" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>236.7</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+      <c r="D95">
+        <v>4</v>
+      </c>
+      <c r="E95">
+        <v>7</v>
+      </c>
+      <c r="F95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>239.1</v>
+      </c>
+      <c r="C96">
+        <v>1.8</v>
+      </c>
+      <c r="D96">
+        <v>6</v>
+      </c>
+      <c r="E96">
+        <v>7.8</v>
+      </c>
+      <c r="F96" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>241.5</v>
+      </c>
+      <c r="C97">
+        <v>0.5</v>
+      </c>
+      <c r="D97">
+        <v>5</v>
+      </c>
+      <c r="E97">
+        <v>5.5</v>
+      </c>
+      <c r="F97" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>243.8</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>3</v>
+      </c>
+      <c r="E98">
+        <v>3</v>
+      </c>
+      <c r="F98" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>246.2</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>8</v>
+      </c>
+      <c r="E99">
+        <v>8</v>
+      </c>
+      <c r="F99" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>248.6</v>
+      </c>
+      <c r="C100">
+        <v>0.5</v>
+      </c>
+      <c r="D100">
+        <v>4</v>
+      </c>
+      <c r="E100">
+        <v>4.5</v>
+      </c>
+      <c r="F100" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>250.9</v>
+      </c>
+      <c r="C101">
+        <v>1.2</v>
+      </c>
+      <c r="D101">
+        <v>7</v>
+      </c>
+      <c r="E101">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F101" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>253.3</v>
+      </c>
+      <c r="C102">
+        <v>2.5</v>
+      </c>
+      <c r="D102">
+        <v>5</v>
+      </c>
+      <c r="E102">
+        <v>7.5</v>
+      </c>
+      <c r="F102" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>255.7</v>
+      </c>
+      <c r="C103">
+        <v>3.4</v>
+      </c>
+      <c r="D103">
+        <v>6</v>
+      </c>
+      <c r="E103">
+        <v>9.4</v>
+      </c>
+      <c r="F103" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>258.10000000000002</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104">
+        <v>3</v>
+      </c>
+      <c r="E104">
+        <v>5</v>
+      </c>
+      <c r="F104" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>260.39999999999998</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>4</v>
+      </c>
+      <c r="E105">
+        <v>5</v>
+      </c>
+      <c r="F105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>262.8</v>
+      </c>
+      <c r="C106">
+        <v>0.5</v>
+      </c>
+      <c r="D106">
+        <v>7</v>
+      </c>
+      <c r="E106">
+        <v>7.5</v>
+      </c>
+      <c r="F106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>265.10000000000002</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>5</v>
+      </c>
+      <c r="E107">
+        <v>5</v>
+      </c>
+      <c r="F107" t="s">
         <v>6</v>
       </c>
     </row>
